--- a/aq_files/0873.xlsx
+++ b/aq_files/0873.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A test produces p = 0.03. If α = 0.05, what decision is made?</t>
-  </si>
-  <si>
-    <t>What does a small p-value indicate?</t>
-  </si>
-  <si>
-    <t>What does p-value represent in hypothesis testing?</t>
-  </si>
-  <si>
-    <t>What is a critical region?</t>
-  </si>
-  <si>
-    <t>A value falls in rejection region. What happens?</t>
-  </si>
-  <si>
-    <t>What is significance level (α)?</t>
-  </si>
-  <si>
-    <t>If p &gt; α, what is the decision?</t>
-  </si>
-  <si>
-    <t>What does p = 0.5 indicate?</t>
-  </si>
-  <si>
-    <t>Why is p-value important?</t>
-  </si>
-  <si>
-    <t>What happens when p-value is extremely small?</t>
-  </si>
-  <si>
-    <t>What is the rejection region also called?</t>
-  </si>
-  <si>
-    <t>How is critical value determined?</t>
-  </si>
-  <si>
-    <t>A test statistic exceeds critical value. What conclusion is drawn?</t>
-  </si>
-  <si>
-    <t>Why do we compare p-value with α?</t>
-  </si>
-  <si>
-    <t>What does p = 0.001 indicate?</t>
-  </si>
-  <si>
-    <t>A value lies outside critical region. What decision is made?</t>
-  </si>
-  <si>
-    <t>What is the difference between p-value and critical value approach?</t>
-  </si>
-  <si>
-    <t>How does sample size affect p-value?</t>
-  </si>
-  <si>
-    <t>What does “statistically significant” mean?</t>
-  </si>
-  <si>
-    <t>Why is α usually set at 0.05?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,1333 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Order_ID,Order_Date,Year,Quarter,Month,Month_Name,Week,Day_Name,Region,State,City,Product_Category,Sub_Category,Product_Name,Sales_Amount,Profit,Quantity,Discount,Unit_Price,Cost,Shipping_Cost,Shipping_Days,Delivery_Days,Customer_Segment,Customer_ID,Customer_Name,Customer_Age,Customer_Gender,Membership_Level,Payment_Method,Shipping_Mode,Order_Priority,Return_Status,Satisfaction_Score,Marketing_Channel,Sales_Rep,Rep_Region,Target_Sales</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1001,2024-01-05,2024,Q1,1,January,1,Monday,North,Illinois,Chicago,Electronics,Computers,MacBook Pro,1299.99,389.99,1,0.05,1299.99,910.00,15.00,2,3,Corporate,C001,John Smith,45,M,Gold,Credit Card,Standard,High,FALSE,4.8,Email,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1002,2024-01-05,2024,Q1,1,January,1,Monday,North,Illinois,Chicago,Electronics,Accessories,Magic Mouse,79.99,23.99,3,0.10,79.99,56.00,8.50,1,2,Corporate,C001,John Smith,45,M,Gold,PayPal,Express,Medium,FALSE,4.5,Email,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1003,2024-01-06,2024,Q1,1,January,1,Tuesday,South,Texas,Houston,Clothing,Mens,Designer Jeans,89.99,26.99,2,0.00,44.99,63.00,12.00,2,4,Consumer,C002,Sarah Lee,28,F,Silver,Debit Card,Standard,Medium,FALSE,4.2,Social Media,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1004,2024-01-06,2024,Q1,1,January,1,Tuesday,South,Texas,Austin,Electronics,Monitors,27-inch Monitor,299.99,89.99,1,0.15,299.99,210.00,18.00,1,3,Consumer,C003,Michael Brown,32,M,Bronze,Credit Card,Express,High,FALSE,4.9,Search Engine,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1005,2024-01-07,2024,Q1,1,January,1,Wednesday,East,New York,New York,Furniture,Chairs,Executive Chair,399.99,119.99,2,0.05,199.99,280.00,22.00,2,5,Corporate,C004,Emily Davis,52,F,Platinum,Credit Card,Standard,High,FALSE,5.0,Direct Mail,Carol Martinez,East,180000</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1006,2024-01-07,2024,Q1,1,January,1,Wednesday,East,New York,Buffalo,Electronics,Keyboards,Mechanical Keyboard,89.99,26.99,2,0.10,44.99,63.00,10.00,1,3,Consumer,C005,David Wilson,26,M,Bronze,PayPal,Standard,Low,FALSE,3.5,Social Media,Carol Martinez,East,180000</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1007,2024-01-08,2024,Q1,1,January,2,Thursday,West,California,Los Angeles,Clothing,Womens,Leather Jacket,199.99,59.99,1,0.20,199.99,140.00,15.00,2,4,Home Office,C006,Lisa Anderson,34,F,Gold,Debit Card,Express,Medium,FALSE,4.7,Email,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1008,2024-01-08,2024,Q1,1,January,2,Thursday,West,California,San Francisco,Electronics,Tablets,iPad,499.99,149.99,1,0.05,499.99,350.00,20.00,1,2,Corporate,C007,Robert Taylor,41,M,Gold,Credit Card,Standard,High,FALSE,4.9,Search Engine,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1009,2024-01-09,2024,Q1,1,January,2,Friday,North,Illinois,Chicago,Furniture,Lighting,Floor Lamp,79.99,23.99,2,0.00,39.99,56.00,12.00,2,3,Consumer,C008,Jennifer Martinez,38,F,Silver,PayPal,Standard,Low,FALSE,4.0,Email,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1010,2024-01-09,2024,Q1,1,January,2,Friday,North,Michigan,Detroit,Clothing,Mens,Running Shoes,69.99,20.99,1,0.10,69.99,49.00,10.00,1,2,Consumer,C009,William Brown,29,M,Bronze,Debit Card,Express,Medium,TRUE,2.8,Social Media,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1011,2024-01-10,2024,Q1,1,January,2,Saturday,South,Texas,Dallas,Electronics,Computers,Gaming Laptop,1299.99,389.99,1,0.15,1299.99,910.00,25.00,2,4,Corporate,C010,Patricia Davis,35,F,Platinum,Credit Card,Standard,High,FALSE,5.0,Direct Mail,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1012,2024-01-10,2024,Q1,1,January,2,Saturday,East,Pennsylvania,Philadelphia,Electronics,Audio,Headphones,149.99,44.99,2,0.05,74.99,105.00,12.00,1,3,Consumer,C011,Michael Miller,27,M,Silver,PayPal,Express,Medium,FALSE,4.3,Social Media,Carol Martinez,East,180000</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1013,2024-01-11,2024,Q1,1,January,2,Sunday,West,California,San Diego,Clothing,Womens,Wool Coat,189.99,56.99,1,0.20,189.99,133.00,15.00,2,4,Home Office,C012,Linda Wilson,39,F,Gold,Debit Card,Standard,Medium,FALSE,4.5,Email,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1014,2024-01-11,2024,Q1,1,January,2,Sunday,North,Ohio,Columbus,Furniture,Storage,Bookshelf,159.99,47.99,1,0.10,159.99,112.00,18.00,2,5,Corporate,C013,Richard Moore,47,M,Silver,Credit Card,Standard,Medium,FALSE,4.2,Search Engine,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1015,2024-01-12,2024,Q1,1,January,2,Monday,South,Florida,Miami,Electronics,Phones,Smartphone,699.99,209.99,2,0.05,349.99,490.00,12.00,1,3,Consumer,C014,Susan Taylor,31,F,Bronze,Credit Card,Express,High,FALSE,4.8,Social Media,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1016,2024-01-12,2024,Q1,1,January,2,Monday,East,New York,New York,Clothing,Mens,Dress Shirt,59.99,17.99,3,0.00,20.00,42.00,10.00,1,2,Corporate,C015,Thomas Anderson,44,M,Gold,PayPal,Standard,Medium,FALSE,4.4,Email,Carol Martinez,East,180000</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1017,2024-01-13,2024,Q1,1,January,2,Tuesday,West,Oregon,Portland,Electronics,Storage,External SSD,99.99,29.99,1,0.10,99.99,70.00,8.50,1,3,Consumer,C016,Jessica Thomas,33,F,Silver,Debit Card,Standard,Low,FALSE,3.9,Social Media,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1018,2024-01-13,2024,Q1,1,January,2,Tuesday,North,Illinois,Chicago,Clothing,Womens,Hoodie,49.99,14.99,2,0.05,25.00,35.00,12.00,1,2,Consumer,C017,Charles Jackson,25,M,Bronze,PayPal,Express,Medium,TRUE,2.5,Email,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1019,2024-01-14,2024,Q1,1,January,2,Wednesday,South,Texas,Austin,Furniture,Desks,Gaming Desk,349.99,104.99,1,0.15,349.99,245.00,25.00,2,4,Corporate,C018,Sarah White,42,F,Platinum,Credit Card,Standard,High,FALSE,4.9,Direct Mail,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1020,2024-01-14,2024,Q1,1,January,2,Wednesday,East,Massachusetts,Boston,Electronics,Accessories,Webcam,79.99,23.99,2,0.10,39.99,56.00,8.50,1,3,Home Office,C019,Daniel Harris,36,M,Gold,PayPal,Express,Medium,FALSE,4.6,Email,Carol Martinez,East,180000</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1021,2024-02-01,2024,Q1,2,February,5,Thursday,West,Washington,Seattle,Electronics,Docks,Docking Station,129.99,38.99,1,0.00,129.99,91.00,10.00,1,3,Consumer,C020,Matthew Clark,40,F,Silver,Debit Card,Standard,Low,FALSE,4.1,Search Engine,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1022,2024-02-01,2024,Q1,2,February,5,Thursday,North,Minnesota,Minneapolis,Clothing,Mens,Winter Parka,179.99,53.99,1,0.05,179.99,126.00,15.00,2,4,Consumer,C021,Amanda Lewis,48,M,Bronze,Credit Card,Standard,Medium,FALSE,4.3,Social Media,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1023,2024-02-02,2024,Q1,2,February,5,Friday,South,Florida,Orlando,Furniture,Desks,Office Desk,449.99,134.99,1,0.10,449.99,315.00,22.00,2,5,Corporate,C022,James Walker,53,F,Gold,PayPal,Express,High,FALSE,4.9,Email,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1024,2024-02-02,2024,Q1,2,February,5,Friday,East,New Jersey,Newark,Electronics,Cables,USB-C Hub,39.99,11.99,3,0.00,13.33,28.00,8.50,1,2,Consumer,C023,Betty Hall,24,M,Silver,Debit Card,Standard,Low,FALSE,3.8,Social Media,Carol Martinez,East,180000</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1025,2024-02-03,2024,Q1,2,February,5,Saturday,West,California,Los Angeles,Clothing,Mens,Casual Blazer,149.99,44.99,1,0.15,149.99,105.00,12.00,1,3,Home Office,C024,Kevin Young,37,F,Gold,Credit Card,Express,Medium,FALSE,4.7,Email,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1026,2024-02-03,2024,Q1,2,February,5,Saturday,North,Indiana,Indianapolis,Electronics,Accessories,Gaming Mouse,59.99,17.99,2,0.10,29.99,42.00,8.50,1,2,Consumer,C025,Nancy Allen,22,M,Bronze,PayPal,Standard,Medium,TRUE,2.9,Search Engine,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1027,2024-02-04,2024,Q1,2,February,5,Sunday,South,Georgia,Atlanta,Electronics,Printers,Laser Printer,199.99,59.99,1,0.05,199.99,140.00,18.00,1,4,Corporate,C026,Edward King,49,F,Platinum,Debit Card,Standard,High,FALSE,4.8,Direct Mail,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1028,2024-02-04,2024,Q1,2,February,5,Sunday,East,Virginia,Richmond,Furniture,Chairs,Lounge Chair,279.99,83.99,1,0.20,279.99,196.00,22.00,2,5,Consumer,C027,Donna Wright,56,M,Silver,Credit Card,Standard,Medium,FALSE,4.2,Email,Carol Martinez,East,180000</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1029,2024-02-05,2024,Q1,2,February,6,Monday,West,Arizona,Phoenix,Electronics,Batteries,Power Bank,49.99,14.99,4,0.00,12.50,35.00,8.50,1,2,Consumer,C028,George Lopez,30,F,Bronze,PayPal,Express,Low,FALSE,4.0,Social Media,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1030,2024-02-05,2024,Q1,2,February,6,Monday,North,Wisconsin,Milwaukee,Clothing,Accessories,Wool Scarf,24.99,7.49,5,0.10,5.00,17.50,8.50,1,2,Consumer,C029,Sandra Hill,26,M,Silver,Debit Card,Standard,Medium,FALSE,4.1,Email,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1031,2024-02-06,2024,Q1,2,February,6,Tuesday,South,Texas,Houston,Electronics,Audio,Gaming Headset,119.99,35.99,1,0.05,119.99,84.00,12.00,1,3,Corporate,C030,Brian Scott,34,F,Gold,Credit Card,Express,High,FALSE,4.9,Search Engine,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1032,2024-02-06,2024,Q1,2,February,6,Tuesday,East,New York,Rochester,Furniture,Storage,Night Stand,69.99,20.99,2,0.10,34.99,49.00,15.00,2,3,Home Office,C031,Carolyn Adams,44,M,Silver,PayPal,Standard,Medium,FALSE,4.3,Social Media,Carol Martinez,East,180000</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1033,2024-02-07,2024,Q1,2,February,6,Wednesday,West,California,San Jose,Clothing,Mens,Athletic Shoes,109.99,32.99,1,0.15,109.99,77.00,10.00,1,2,Consumer,C032,Frank Baker,29,F,Bronze,Debit Card,Express,Medium,FALSE,4.5,Email,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1034,2024-02-07,2024,Q1,2,February,6,Wednesday,North,Missouri,St Louis,Electronics,Wearables,Smart Watch,199.99,59.99,1,0.05,199.99,140.00,12.00,1,3,Consumer,C033,Ruth Gonzalez,38,M,Silver,Credit Card,Standard,High,FALSE,4.7,Direct Mail,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1035,2024-02-08,2024,Q1,2,February,6,Thursday,South,Florida,Tampa,Electronics,Audio,Bluetooth Speaker,79.99,23.99,2,0.10,39.99,56.00,10.00,1,3,Corporate,C034,Peter Nelson,31,F,Gold,PayPal,Standard,Medium,FALSE,4.4,Email,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1036,2024-02-08,2024,Q1,2,February,6,Thursday,East,Pennsylvania,Pittsburgh,Clothing,Womens,Cashmere Sweater,99.99,29.99,1,0.00,99.99,70.00,12.00,1,3,Consumer,C035,Kimberly Carter,41,M,Bronze,Debit Card,Express,Low,TRUE,2.7,Social Media,Carol Martinez,East,180000</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1037,2024-02-09,2024,Q1,2,February,6,Friday,West,Oregon,Eugene,Furniture,Storage,Bookshelf,129.99,38.99,1,0.05,129.99,91.00,18.00,2,4,Home Office,C036,Steven Mitchell,46,F,Silver,Credit Card,Standard,Medium,FALSE,4.2,Search Engine,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1038,2024-02-09,2024,Q1,2,February,6,Friday,North,Iowa,Des Moines,Electronics,Networking,Mesh Router,99.99,29.99,1,0.10,99.99,70.00,10.00,1,2,Consumer,C037,Laura Perez,28,M,Gold,PayPal,Standard,Low,FALSE,4.0,Email,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1039,2024-02-10,2024,Q1,2,February,6,Saturday,South,Texas,San Antonio,Clothing,Mens,Golf Polo,44.99,13.49,3,0.15,15.00,31.50,8.50,1,2,Consumer,C038,Paul Roberts,23,F,Bronze,Debit Card,Express,Medium,FALSE,4.3,Social Media,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1040,2024-02-10,2024,Q1,2,February,6,Saturday,West,Washington,Spokane,Electronics,Components,Graphics Card,499.99,149.99,1,0.20,499.99,350.00,18.00,2,4,Corporate,C039,Mary Turner,43,M,Platinum,Credit Card,Standard,High,FALSE,5.0,Direct Mail,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1041,2024-03-01,2024,Q1,3,March,9,Sunday,North,Illinois,Chicago,Electronics,Computers,Desktop PC,999.99,299.99,1,0.05,999.99,700.00,25.00,2,3,Corporate,C040,Daniel Phillips,50,F,Gold,Credit Card,Standard,High,FALSE,4.9,Email,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1042,2024-03-01,2024,Q1,3,March,9,Sunday,South,Texas,Austin,Clothing,Womens,Yoga Pants,49.99,14.99,2,0.00,25.00,35.00,8.50,1,2,Consumer,C041,Lisa Campbell,27,M,Silver,PayPal,Express,Medium,FALSE,4.4,Social Media,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1043,2024-03-02,2024,Q1,3,March,9,Monday,East,New York,New York,Furniture,Tables,Coffee Table,249.99,74.99,1,0.10,249.99,175.00,22.00,2,4,Corporate,C042,Ronald Parker,55,F,Platinum,Debit Card,Standard,High,FALSE,4.8,Direct Mail,Carol Martinez,East,180000</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1044,2024-03-02,2024,Q1,3,March,9,Monday,West,California,Los Angeles,Electronics,Smart Home,Smart Speaker,89.99,26.99,2,0.00,45.00,63.00,10.00,1,2,Home Office,C043,Deborah Evans,34,M,Gold,Credit Card,Express,Medium,FALSE,4.6,Email,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1045,2024-03-03,2024,Q1,3,March,9,Tuesday,North,Michigan,Detroit,Clothing,Accessories,Baseball Cap,19.99,5.99,4,0.05,5.00,14.00,8.50,1,2,Consumer,C044,Joseph Edwards,19,F,Bronze,PayPal,Standard,Low,FALSE,3.5,Search Engine,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1046,2024-03-03,2024,Q1,3,March,9,Tuesday,South,Florida,Miami,Electronics,Drones,Quadcopter,349.99,104.99,1,0.10,349.99,245.00,18.00,1,3,Corporate,C045,Barbara Collins,38,M,Gold,Debit Card,Standard,High,FALSE,4.9,Email,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1047,2024-03-04,2024,Q1,3,March,9,Wednesday,East,Pennsylvania,Philadelphia,Furniture,Decor,Wall Mirror,59.99,17.99,2,0.00,30.00,42.00,12.00,1,2,Consumer,C046,Mark Stewart,42,F,Silver,Credit Card,Express,Medium,FALSE,4.2,Social Media,Carol Martinez,East,180000</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1048,2024-03-04,2024,Q1,3,March,9,Wednesday,West,Oregon,Portland,Clothing,Mens,Flannel Shirt,49.99,14.99,2,0.10,25.00,35.00,10.00,1,3,Home Office,C047,Carol Morris,35,M,Gold,PayPal,Standard,Low,FALSE,4.1,Email,David Lee,West,200000</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1049,2024-03-05,2024,Q1,3,March,10,Thursday,North,Ohio,Columbus,Electronics,Streaming,Streaming Stick,29.99,8.99,3,0.05,10.00,21.00,8.50,1,2,Consumer,C048,Raymond Rogers,24,F,Bronze,Debit Card,Standard,Medium,TRUE,2.6,Search Engine,Alice Johnson,North,150000</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1050,2024-03-05,2024,Q1,3,March,10,Thursday,South,Georgia,Atlanta,Clothing,Womens,Leggings,29.99,8.99,4,0.00,7.50,21.00,8.50,1,2,Consumer,C049,Anna Reed,22,M,Silver,Credit Card,Express,Medium,FALSE,4.3,Social Media,Bob Williams,South,120000</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3051,2024-02-11,West,California,Los Angeles,Electronics,Monitors,Ultrawide Monitor,549.99,2,549.98,0.15,22.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3052,2024-02-11,North,Illinois,Chicago,Clothing,Mens,Denim Jacket,89.99,5,224.98,0.10,12.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3053,2024-02-12,South,Texas,Houston,Furniture,Chairs,Gaming Chair,299.99,2,299.98,0.05,22.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3054,2024-02-12,East,New York,Buffalo,Electronics,Audio,Portable Speaker,79.99,4,159.98,0.00,10.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3055,2024-02-13,West,Washington,Seattle,Clothing,Womens,Rain Jacket,129.99,3,194.98,0.15,12.00,Home Office</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3056,2024-02-13,North,Minnesota,Minneapolis,Electronics,Storage,Portable SSD,89.99,5,224.98,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3057,2024-02-14,South,Florida,Orlando,Electronics,Phones,Smartphone Case,29.99,15,224.85,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3058,2024-02-14,East,Massachusetts,Boston,Furniture,Lighting,Desk Lamp,59.99,6,179.97,0.05,12.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3059,2024-02-15,West,California,San Diego,Clothing,Accessories,Leather Belt,39.99,8,159.96,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3060,2024-02-15,North,Ohio,Columbus,Electronics,Accessories,Phone Stand,19.99,12,119.94,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Create a Sales Dashboard with a Title 'Sales Performance Dashboard', a company logo placeholder, and a date range filter. What is the total sales for January 2024?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Create KPI Cards for Total Sales, Total Profit, Total Quantity, and Average Discount. Format them with appropriate icons and conditional formatting.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Create a Bar Chart showing Sales by Product Category with a goal line showing target sales. Add a title 'Category Performance'.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Create a Map visual showing Sales by State with color intensity representing sales volume. Add a title 'Geographic Sales Distribution'.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Create a Line Chart showing Monthly Sales Trend with a forecast for the next 3 months. Add a title 'Sales Trend &amp; Forecast'.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Create a Treemap showing Sales by Category and Sub-Category. Add a title 'Product Hierarchy Performance'.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Create a Scatter Plot showing Profit vs Sales with Quantity as bubble size and Category as color. Add a title 'Profitability Matrix'.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Create a Gauge visual showing Profit vs Target ($8,000). Add a title 'Profit vs Target'.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Create a Donut Chart showing Sales by Customer Segment. Add a title 'Customer Segment Distribution'.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Create a Stacked Bar Chart showing Sales by Region and Customer Segment. Add a title 'Regional Segment Analysis'.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Create a Matrix visual showing Sales by Region (rows) and Month (columns) with conditional formatting. Add a title 'Monthly Regional Matrix'.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Create a Decomposition Tree showing Sales breakdown by Region → Category → Sub_Category → Product. Add a title 'Sales Decomposition'.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Create a Q&amp;A Visual that allows users to ask questions like 'total sales by region' or 'top 5 products'. Add a title 'Ask Questions'.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Create a Bookmark for a filtered view showing only Electronics category sales. Add navigation buttons to switch between views.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Create a Drillthrough page that shows detailed order information when clicking on a region. Add a title 'Order Details'.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Create a Tooltip page that shows product details when hovering over a bar chart. Add a title 'Product Details Tooltip'.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Create a What-If Parameter for Discount % to see impact on profit. Add a slicer to control the parameter.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Create a Mobile Layout optimized for phone viewing. Rearrange visuals for portrait orientation.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Create a Dashboard with cross-filtering between all visuals. Add a clear slicer button to reset filters.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a Performance Analyzer to measure dashboard load time. Identify which visual takes longest to render.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>